--- a/Config/Datas/skill.xlsx
+++ b/Config/Datas/skill.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="87">
   <si>
     <t>##var</t>
   </si>
@@ -245,6 +245,9 @@
   </si>
   <si>
     <t>chongzhuang</t>
+  </si>
+  <si>
+    <t>h_spirit_immune</t>
   </si>
   <si>
     <t>school_id</t>
@@ -299,14 +302,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -762,148 +758,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1256,11 +1252,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S39"/>
+  <dimension ref="A1:S41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="21.25" customWidth="1"/>
-    <col min="4" max="4" width="12.875" customWidth="1"/>
+    <col min="3" max="4" width="12.875" customWidth="1"/>
     <col min="18" max="18" width="14" customWidth="1"/>
     <col min="19" max="19" width="15.125" customWidth="1"/>
   </cols>
@@ -3344,6 +3340,17 @@
       </c>
       <c r="S39" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="41" spans="2:19">
+      <c r="B41" t="s">
+        <v>72</v>
+      </c>
+      <c r="D41" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -3363,16 +3370,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D1" t="s">
         <v>12</v>
       </c>
       <c r="E1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3414,16 +3421,16 @@
         <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3431,7 +3438,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
         <v>31</v>
@@ -3445,7 +3452,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
         <v>33</v>
@@ -3459,7 +3466,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
         <v>31</v>
@@ -3488,22 +3495,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F1" t="s">
         <v>1</v>
       </c>
       <c r="G1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3520,7 +3527,7 @@
         <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F2" t="s">
         <v>20</v>
@@ -3557,22 +3564,22 @@
         <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F4" t="s">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -3583,7 +3590,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
         <v>31</v>
@@ -3603,7 +3610,7 @@
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
         <v>31</v>
@@ -3623,7 +3630,7 @@
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
         <v>31</v>
@@ -3643,7 +3650,7 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
         <v>31</v>

--- a/Config/Datas/skill.xlsx
+++ b/Config/Datas/skill.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="88">
   <si>
     <t>##var</t>
   </si>
@@ -248,6 +248,9 @@
   </si>
   <si>
     <t>h_spirit_immune</t>
+  </si>
+  <si>
+    <t>player_burst_h_voice</t>
   </si>
   <si>
     <t>school_id</t>
@@ -1252,7 +1255,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S41"/>
+  <dimension ref="A1:S42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="21.25" customWidth="1"/>
@@ -3351,6 +3354,17 @@
       </c>
       <c r="E41" t="s">
         <v>72</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19">
+      <c r="B42" t="s">
+        <v>73</v>
+      </c>
+      <c r="D42" t="b">
+        <v>1</v>
+      </c>
+      <c r="E42" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -3370,16 +3384,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D1" t="s">
         <v>12</v>
       </c>
       <c r="E1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3421,16 +3435,16 @@
         <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3438,7 +3452,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
         <v>31</v>
@@ -3452,7 +3466,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
         <v>33</v>
@@ -3466,7 +3480,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
         <v>31</v>
@@ -3495,22 +3509,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F1" t="s">
         <v>1</v>
       </c>
       <c r="G1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3527,7 +3541,7 @@
         <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F2" t="s">
         <v>20</v>
@@ -3564,22 +3578,22 @@
         <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F4" t="s">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -3590,7 +3604,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
         <v>31</v>
@@ -3610,7 +3624,7 @@
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
         <v>31</v>
@@ -3630,7 +3644,7 @@
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E7" t="s">
         <v>31</v>
@@ -3650,7 +3664,7 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E8" t="s">
         <v>31</v>

--- a/Config/Datas/skill.xlsx
+++ b/Config/Datas/skill.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="89">
   <si>
     <t>##var</t>
   </si>
@@ -227,6 +227,9 @@
   </si>
   <si>
     <t>DefaultAttackPre,0.5|DefaultAttackTime,0.4</t>
+  </si>
+  <si>
+    <t>force_dash_push_down</t>
   </si>
   <si>
     <t>default_h_attack</t>
@@ -1255,11 +1258,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S42"/>
+  <dimension ref="A1:S43"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="21.25" customWidth="1"/>
     <col min="3" max="4" width="12.875" customWidth="1"/>
+    <col min="9" max="9" width="14.125" customWidth="1"/>
+    <col min="12" max="12" width="22.625" customWidth="1"/>
     <col min="18" max="18" width="14" customWidth="1"/>
     <col min="19" max="19" width="15.125" customWidth="1"/>
   </cols>
@@ -3121,124 +3126,112 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="2:19">
-      <c r="B35" t="s">
+    <row r="34" spans="2:19">
+      <c r="B34" t="s">
         <v>66</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C34" t="s">
         <v>66</v>
       </c>
-      <c r="D35" t="b">
-        <v>0</v>
-      </c>
-      <c r="E35" t="s">
-        <v>31</v>
-      </c>
-      <c r="F35" t="s">
-        <v>31</v>
-      </c>
-      <c r="G35" t="b">
-        <v>0</v>
-      </c>
-      <c r="H35" t="b">
-        <v>1</v>
-      </c>
-      <c r="I35" t="b">
-        <v>1</v>
-      </c>
-      <c r="J35" t="b">
-        <v>0</v>
-      </c>
-      <c r="K35">
+      <c r="D34" t="b">
+        <v>0</v>
+      </c>
+      <c r="G34" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" t="b">
+        <v>0</v>
+      </c>
+      <c r="I34" t="b">
+        <v>1</v>
+      </c>
+      <c r="J34" t="b">
+        <v>0</v>
+      </c>
+      <c r="K34">
         <v>2</v>
       </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35" t="s">
-        <v>31</v>
-      </c>
-      <c r="N35">
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34" t="s">
+        <v>33</v>
+      </c>
+      <c r="N34">
         <v>10</v>
       </c>
-      <c r="O35">
-        <v>0</v>
-      </c>
-      <c r="P35">
-        <v>1</v>
-      </c>
-      <c r="Q35">
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>1</v>
+      </c>
+      <c r="Q34">
         <v>0.1</v>
       </c>
-      <c r="R35" t="s">
+    </row>
+    <row r="36" spans="2:19">
+      <c r="B36" t="s">
+        <v>67</v>
+      </c>
+      <c r="C36" t="s">
+        <v>67</v>
+      </c>
+      <c r="D36" t="b">
+        <v>0</v>
+      </c>
+      <c r="E36" t="s">
+        <v>31</v>
+      </c>
+      <c r="F36" t="s">
+        <v>31</v>
+      </c>
+      <c r="G36" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" t="b">
+        <v>1</v>
+      </c>
+      <c r="I36" t="b">
+        <v>1</v>
+      </c>
+      <c r="J36" t="b">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>2</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36" t="s">
+        <v>31</v>
+      </c>
+      <c r="N36">
+        <v>10</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>1</v>
+      </c>
+      <c r="Q36">
+        <v>0.1</v>
+      </c>
+      <c r="R36" t="s">
         <v>65</v>
       </c>
-      <c r="S35" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="37" spans="2:19">
-      <c r="B37" t="s">
-        <v>67</v>
-      </c>
-      <c r="C37" t="s">
-        <v>68</v>
-      </c>
-      <c r="D37" t="b">
-        <v>0</v>
-      </c>
-      <c r="E37" t="s">
-        <v>31</v>
-      </c>
-      <c r="F37" t="s">
-        <v>31</v>
-      </c>
-      <c r="G37" t="b">
-        <v>0</v>
-      </c>
-      <c r="H37" t="b">
-        <v>0</v>
-      </c>
-      <c r="I37" t="b">
-        <v>1</v>
-      </c>
-      <c r="J37" t="b">
-        <v>0</v>
-      </c>
-      <c r="K37">
-        <v>10</v>
-      </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-      <c r="M37" t="s">
-        <v>31</v>
-      </c>
-      <c r="N37">
-        <v>5</v>
-      </c>
-      <c r="O37">
-        <v>0</v>
-      </c>
-      <c r="P37">
-        <v>5</v>
-      </c>
-      <c r="Q37">
-        <v>0.1</v>
-      </c>
-      <c r="R37" t="s">
-        <v>31</v>
-      </c>
-      <c r="S37" t="s">
+      <c r="S36" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="38" spans="2:19">
       <c r="B38" t="s">
+        <v>68</v>
+      </c>
+      <c r="C38" t="s">
         <v>69</v>
-      </c>
-      <c r="C38" t="s">
-        <v>68</v>
       </c>
       <c r="D38" t="b">
         <v>0</v>
@@ -3294,7 +3287,7 @@
         <v>70</v>
       </c>
       <c r="C39" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D39" t="b">
         <v>0</v>
@@ -3318,7 +3311,7 @@
         <v>0</v>
       </c>
       <c r="K39">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -3333,7 +3326,7 @@
         <v>0</v>
       </c>
       <c r="P39">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="Q39">
         <v>0.1</v>
@@ -3345,15 +3338,60 @@
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="2:19">
-      <c r="B41" t="s">
+    <row r="40" spans="2:19">
+      <c r="B40" t="s">
+        <v>71</v>
+      </c>
+      <c r="C40" t="s">
         <v>72</v>
       </c>
-      <c r="D41" t="b">
-        <v>1</v>
-      </c>
-      <c r="E41" t="s">
-        <v>72</v>
+      <c r="D40" t="b">
+        <v>0</v>
+      </c>
+      <c r="E40" t="s">
+        <v>31</v>
+      </c>
+      <c r="F40" t="s">
+        <v>31</v>
+      </c>
+      <c r="G40" t="b">
+        <v>0</v>
+      </c>
+      <c r="H40" t="b">
+        <v>0</v>
+      </c>
+      <c r="I40" t="b">
+        <v>1</v>
+      </c>
+      <c r="J40" t="b">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>5</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40" t="s">
+        <v>31</v>
+      </c>
+      <c r="N40">
+        <v>5</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
+        <v>1.5</v>
+      </c>
+      <c r="Q40">
+        <v>0.1</v>
+      </c>
+      <c r="R40" t="s">
+        <v>31</v>
+      </c>
+      <c r="S40" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="42" spans="2:19">
@@ -3365,6 +3403,17 @@
       </c>
       <c r="E42" t="s">
         <v>73</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19">
+      <c r="B43" t="s">
+        <v>74</v>
+      </c>
+      <c r="D43" t="b">
+        <v>1</v>
+      </c>
+      <c r="E43" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -3384,16 +3433,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D1" t="s">
         <v>12</v>
       </c>
       <c r="E1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3435,16 +3484,16 @@
         <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3452,7 +3501,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
         <v>31</v>
@@ -3466,7 +3515,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
         <v>33</v>
@@ -3480,7 +3529,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
         <v>31</v>
@@ -3509,22 +3558,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F1" t="s">
         <v>1</v>
       </c>
       <c r="G1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3541,7 +3590,7 @@
         <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F2" t="s">
         <v>20</v>
@@ -3578,22 +3627,22 @@
         <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F4" t="s">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -3604,7 +3653,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E5" t="s">
         <v>31</v>
@@ -3624,7 +3673,7 @@
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E6" t="s">
         <v>31</v>
@@ -3644,7 +3693,7 @@
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E7" t="s">
         <v>31</v>
@@ -3664,7 +3713,7 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
         <v>31</v>

--- a/Config/Datas/skill.xlsx
+++ b/Config/Datas/skill.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="90">
   <si>
     <t>##var</t>
   </si>
@@ -254,6 +254,9 @@
   </si>
   <si>
     <t>player_burst_h_voice</t>
+  </si>
+  <si>
+    <t>npc_grapple_push_player</t>
   </si>
   <si>
     <t>school_id</t>
@@ -764,154 +767,153 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1258,7 +1260,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S43"/>
+  <dimension ref="A1:S44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="21.25" customWidth="1"/>
@@ -1297,7 +1299,7 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
       <c r="K1" t="s">
@@ -1356,7 +1358,7 @@
       <c r="I2" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" t="s">
         <v>21</v>
       </c>
       <c r="K2" t="s">
@@ -1412,7 +1414,7 @@
       <c r="I3" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" t="s">
         <v>28</v>
       </c>
       <c r="K3" t="s">
@@ -1471,7 +1473,7 @@
       <c r="I4" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="J4" t="s">
         <v>9</v>
       </c>
       <c r="K4" t="s">
@@ -3414,6 +3416,47 @@
       </c>
       <c r="E43" t="s">
         <v>74</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19">
+      <c r="B44" t="s">
+        <v>75</v>
+      </c>
+      <c r="C44" t="s">
+        <v>75</v>
+      </c>
+      <c r="D44" t="b">
+        <v>0</v>
+      </c>
+      <c r="G44" t="b">
+        <v>0</v>
+      </c>
+      <c r="H44" t="b">
+        <v>0</v>
+      </c>
+      <c r="I44" t="b">
+        <v>1</v>
+      </c>
+      <c r="J44" t="b">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>1</v>
+      </c>
+      <c r="Q44">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3433,16 +3476,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D1" t="s">
         <v>12</v>
       </c>
       <c r="E1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3484,16 +3527,16 @@
         <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3501,7 +3544,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
         <v>31</v>
@@ -3515,7 +3558,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
         <v>33</v>
@@ -3529,7 +3572,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
         <v>31</v>
@@ -3558,22 +3601,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F1" t="s">
         <v>1</v>
       </c>
       <c r="G1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3590,7 +3633,7 @@
         <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F2" t="s">
         <v>20</v>
@@ -3627,22 +3670,22 @@
         <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F4" t="s">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -3653,7 +3696,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
         <v>31</v>
@@ -3673,7 +3716,7 @@
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E6" t="s">
         <v>31</v>
@@ -3693,7 +3736,7 @@
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
         <v>31</v>
@@ -3713,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
         <v>31</v>

--- a/Config/Datas/skill.xlsx
+++ b/Config/Datas/skill.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="91">
   <si>
     <t>##var</t>
   </si>
@@ -254,6 +254,9 @@
   </si>
   <si>
     <t>player_burst_h_voice</t>
+  </si>
+  <si>
+    <t>player_burst_milk</t>
   </si>
   <si>
     <t>npc_grapple_push_player</t>
@@ -1260,7 +1263,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S44"/>
+  <dimension ref="A1:S45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="21.25" customWidth="1"/>
@@ -3422,40 +3425,51 @@
       <c r="B44" t="s">
         <v>75</v>
       </c>
-      <c r="C44" t="s">
+      <c r="D44" t="b">
+        <v>1</v>
+      </c>
+      <c r="E44" t="s">
         <v>75</v>
       </c>
-      <c r="D44" t="b">
-        <v>0</v>
-      </c>
-      <c r="G44" t="b">
-        <v>0</v>
-      </c>
-      <c r="H44" t="b">
-        <v>0</v>
-      </c>
-      <c r="I44" t="b">
-        <v>1</v>
-      </c>
-      <c r="J44" t="b">
-        <v>0</v>
-      </c>
-      <c r="K44">
-        <v>0</v>
-      </c>
-      <c r="L44">
-        <v>0</v>
-      </c>
-      <c r="N44">
-        <v>0</v>
-      </c>
-      <c r="O44">
-        <v>0</v>
-      </c>
-      <c r="P44">
-        <v>1</v>
-      </c>
-      <c r="Q44">
+    </row>
+    <row r="45" spans="2:19">
+      <c r="B45" t="s">
+        <v>76</v>
+      </c>
+      <c r="C45" t="s">
+        <v>76</v>
+      </c>
+      <c r="D45" t="b">
+        <v>0</v>
+      </c>
+      <c r="G45" t="b">
+        <v>0</v>
+      </c>
+      <c r="H45" t="b">
+        <v>0</v>
+      </c>
+      <c r="I45" t="b">
+        <v>1</v>
+      </c>
+      <c r="J45" t="b">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>0</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>1</v>
+      </c>
+      <c r="Q45">
         <v>0</v>
       </c>
     </row>
@@ -3476,16 +3490,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D1" t="s">
         <v>12</v>
       </c>
       <c r="E1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3527,16 +3541,16 @@
         <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3544,7 +3558,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
         <v>31</v>
@@ -3558,7 +3572,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
         <v>33</v>
@@ -3572,7 +3586,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
         <v>31</v>
@@ -3601,22 +3615,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F1" t="s">
         <v>1</v>
       </c>
       <c r="G1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3633,7 +3647,7 @@
         <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F2" t="s">
         <v>20</v>
@@ -3670,22 +3684,22 @@
         <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F4" t="s">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -3696,7 +3710,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
         <v>31</v>
@@ -3716,7 +3730,7 @@
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
         <v>31</v>
@@ -3736,7 +3750,7 @@
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E7" t="s">
         <v>31</v>
@@ -3756,7 +3770,7 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
         <v>31</v>

--- a/Config/Datas/skill.xlsx
+++ b/Config/Datas/skill.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="92">
   <si>
     <t>##var</t>
   </si>
@@ -260,6 +260,9 @@
   </si>
   <si>
     <t>npc_grapple_push_player</t>
+  </si>
+  <si>
+    <t>shoot_knife</t>
   </si>
   <si>
     <t>school_id</t>
@@ -1263,7 +1266,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S45"/>
+  <dimension ref="A1:S47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="21.25" customWidth="1"/>
@@ -3470,6 +3473,56 @@
         <v>1</v>
       </c>
       <c r="Q45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19">
+      <c r="B47" t="s">
+        <v>77</v>
+      </c>
+      <c r="C47" t="s">
+        <v>77</v>
+      </c>
+      <c r="D47" t="b">
+        <v>0</v>
+      </c>
+      <c r="E47" t="s">
+        <v>31</v>
+      </c>
+      <c r="F47" t="s">
+        <v>31</v>
+      </c>
+      <c r="G47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I47" t="b">
+        <v>1</v>
+      </c>
+      <c r="J47" t="b">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47" t="s">
+        <v>31</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
         <v>0</v>
       </c>
     </row>
@@ -3490,16 +3543,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D1" t="s">
         <v>12</v>
       </c>
       <c r="E1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3541,16 +3594,16 @@
         <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
         <v>12</v>
       </c>
       <c r="E4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3558,7 +3611,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
         <v>31</v>
@@ -3572,7 +3625,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
         <v>33</v>
@@ -3586,7 +3639,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
         <v>31</v>
@@ -3615,22 +3668,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F1" t="s">
         <v>1</v>
       </c>
       <c r="G1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3647,7 +3700,7 @@
         <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F2" t="s">
         <v>20</v>
@@ -3684,22 +3737,22 @@
         <v>29</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F4" t="s">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -3710,7 +3763,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E5" t="s">
         <v>31</v>
@@ -3730,7 +3783,7 @@
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E6" t="s">
         <v>31</v>
@@ -3750,7 +3803,7 @@
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
         <v>31</v>
@@ -3770,7 +3823,7 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E8" t="s">
         <v>31</v>

--- a/Config/Datas/skill.xlsx
+++ b/Config/Datas/skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17205"/>
   </bookViews>
   <sheets>
     <sheet name="entity_skill" sheetId="1" r:id="rId1"/>

--- a/Config/Datas/skill.xlsx
+++ b/Config/Datas/skill.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="106">
   <si>
     <t>##var</t>
   </si>
@@ -296,6 +296,15 @@
   </si>
   <si>
     <t>player_fq_dash_assult</t>
+  </si>
+  <si>
+    <t>ex_zhazhi_01</t>
+  </si>
+  <si>
+    <t>ex_zhazhi_02</t>
+  </si>
+  <si>
+    <t>ex_zhazhi_03</t>
   </si>
   <si>
     <t>school_id</t>
@@ -1299,11 +1308,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U53"/>
+  <dimension ref="A1:U57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="21.25" customWidth="1"/>
     <col min="3" max="6" width="12.875" customWidth="1"/>
+    <col min="7" max="7" width="18.625" customWidth="1"/>
     <col min="11" max="11" width="14.125" customWidth="1"/>
     <col min="14" max="14" width="22.625" customWidth="1"/>
     <col min="15" max="15" width="17.75" customWidth="1"/>
@@ -3803,6 +3813,30 @@
       </c>
       <c r="S53">
         <v>0.1</v>
+      </c>
+    </row>
+    <row r="55" spans="2:19">
+      <c r="B55" t="s">
+        <v>89</v>
+      </c>
+      <c r="F55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="2:19">
+      <c r="B56" t="s">
+        <v>90</v>
+      </c>
+      <c r="F56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="2:19">
+      <c r="B57" t="s">
+        <v>91</v>
+      </c>
+      <c r="F57" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3822,16 +3856,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D1" t="s">
         <v>14</v>
       </c>
       <c r="E1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3873,16 +3907,16 @@
         <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3890,7 +3924,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
         <v>34</v>
@@ -3904,7 +3938,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="D6" t="s">
         <v>36</v>
@@ -3918,7 +3952,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
         <v>34</v>
@@ -3947,22 +3981,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F1" t="s">
         <v>1</v>
       </c>
       <c r="G1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3979,7 +4013,7 @@
         <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F2" t="s">
         <v>22</v>
@@ -4016,22 +4050,22 @@
         <v>31</v>
       </c>
       <c r="B4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F4" t="s">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -4042,7 +4076,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E5" t="s">
         <v>34</v>
@@ -4062,7 +4096,7 @@
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E6" t="s">
         <v>34</v>
@@ -4082,7 +4116,7 @@
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E7" t="s">
         <v>34</v>
@@ -4102,7 +4136,7 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E8" t="s">
         <v>34</v>

--- a/Config/Datas/skill.xlsx
+++ b/Config/Datas/skill.xlsx
@@ -1033,7 +1033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V57"/>
+  <dimension ref="A1:V58"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="21.25" customWidth="1" min="2" max="2"/>
@@ -3554,6 +3554,51 @@
       </c>
       <c r="F57" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>use_human_weapon</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>use_human_weapon</t>
+        </is>
+      </c>
+      <c r="F58" t="b">
+        <v>0</v>
+      </c>
+      <c r="J58" t="b">
+        <v>0</v>
+      </c>
+      <c r="K58" t="b">
+        <v>0</v>
+      </c>
+      <c r="L58" t="b">
+        <v>1</v>
+      </c>
+      <c r="M58" t="b">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/skill.xlsx
+++ b/Config/Datas/skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17655" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="entity_skill" sheetId="1" r:id="rId1"/>

--- a/Config/Datas/skill.xlsx
+++ b/Config/Datas/skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="2"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="entity_skill" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="123">
   <si>
     <t>##var</t>
   </si>
@@ -341,6 +341,18 @@
   </si>
   <si>
     <t>b_lamp_extra_vision</t>
+  </si>
+  <si>
+    <t>rune_weiyi_regen_ooc</t>
+  </si>
+  <si>
+    <t>b_weiyi_regen_ooc</t>
+  </si>
+  <si>
+    <t>rune_weiyi_more_layer</t>
+  </si>
+  <si>
+    <t>b_weiyi_more_layer</t>
   </si>
   <si>
     <t>school_id</t>
@@ -1347,7 +1359,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U64"/>
+  <dimension ref="A1:U67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="21.25" customWidth="1"/>
@@ -3612,6 +3624,28 @@
         <v>103</v>
       </c>
     </row>
+    <row r="66" spans="2:7">
+      <c r="B66" t="s">
+        <v>104</v>
+      </c>
+      <c r="F66" t="b">
+        <v>1</v>
+      </c>
+      <c r="G66" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7">
+      <c r="B67" t="s">
+        <v>106</v>
+      </c>
+      <c r="F67" t="b">
+        <v>1</v>
+      </c>
+      <c r="G67" t="s">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -3629,16 +3663,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D1" t="s">
         <v>14</v>
       </c>
       <c r="E1" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3680,16 +3714,16 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3697,7 +3731,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E5">
         <v>10</v>
@@ -3708,7 +3742,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D6" t="s">
         <v>36</v>
@@ -3722,7 +3756,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E7">
         <v>30</v>
@@ -3748,22 +3782,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C1" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D1" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E1" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F1" t="s">
         <v>1</v>
       </c>
       <c r="G1" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3780,7 +3814,7 @@
         <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="F2" t="s">
         <v>22</v>
@@ -3817,22 +3851,22 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F4" t="s">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -3843,7 +3877,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F5" t="s">
         <v>67</v>
@@ -3860,7 +3894,7 @@
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F6" t="s">
         <v>37</v>
@@ -3877,7 +3911,7 @@
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F7" t="s">
         <v>39</v>
@@ -3894,7 +3928,7 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F8" t="s">
         <v>34</v>
@@ -3914,7 +3948,7 @@
         <v>96</v>
       </c>
       <c r="E9" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F9" t="s">
         <v>95</v>

--- a/Config/Datas/skill.xlsx
+++ b/Config/Datas/skill.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="125">
   <si>
     <t>##var</t>
   </si>
@@ -353,6 +353,12 @@
   </si>
   <si>
     <t>b_weiyi_more_layer</t>
+  </si>
+  <si>
+    <t>rune_perfect_dodge_weiyi</t>
+  </si>
+  <si>
+    <t>passive_perfect_dodge_weiyi</t>
   </si>
   <si>
     <t>school_id</t>
@@ -1359,7 +1365,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U67"/>
+  <dimension ref="A1:U68"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="21.25" customWidth="1"/>
@@ -3646,6 +3652,17 @@
         <v>107</v>
       </c>
     </row>
+    <row r="68" spans="2:7">
+      <c r="B68" t="s">
+        <v>108</v>
+      </c>
+      <c r="F68" t="b">
+        <v>1</v>
+      </c>
+      <c r="G68" t="s">
+        <v>109</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -3663,16 +3680,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D1" t="s">
         <v>14</v>
       </c>
       <c r="E1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -3714,16 +3731,16 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3731,7 +3748,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E5">
         <v>10</v>
@@ -3742,7 +3759,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D6" t="s">
         <v>36</v>
@@ -3756,7 +3773,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E7">
         <v>30</v>
@@ -3782,22 +3799,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F1" t="s">
         <v>1</v>
       </c>
       <c r="G1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -3814,7 +3831,7 @@
         <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F2" t="s">
         <v>22</v>
@@ -3851,22 +3868,22 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F4" t="s">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -3877,7 +3894,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F5" t="s">
         <v>67</v>
@@ -3894,7 +3911,7 @@
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F6" t="s">
         <v>37</v>
@@ -3911,7 +3928,7 @@
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F7" t="s">
         <v>39</v>
@@ -3928,7 +3945,7 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F8" t="s">
         <v>34</v>
@@ -3948,7 +3965,7 @@
         <v>96</v>
       </c>
       <c r="E9" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F9" t="s">
         <v>95</v>

--- a/Config/Datas/skill.xlsx
+++ b/Config/Datas/skill.xlsx
@@ -1033,7 +1033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U68"/>
+  <dimension ref="A1:U70"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="21.25" customWidth="1" min="2" max="2"/>
@@ -2891,7 +2891,6 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="B36" t="inlineStr">
         <is>
@@ -2942,7 +2941,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="B38" t="inlineStr">
         <is>
@@ -3078,7 +3076,6 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="41"/>
     <row r="42">
       <c r="B42" t="inlineStr">
         <is>
@@ -3169,7 +3166,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46"/>
     <row r="47">
       <c r="B47" t="inlineStr">
         <is>
@@ -3265,7 +3261,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49"/>
     <row r="50">
       <c r="B50" t="inlineStr">
         <is>
@@ -3531,7 +3526,6 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="55"/>
     <row r="56">
       <c r="B56" t="inlineStr">
         <is>
@@ -3677,7 +3671,6 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="61"/>
     <row r="62">
       <c r="B62" t="inlineStr">
         <is>
@@ -3740,7 +3733,6 @@
         </is>
       </c>
     </row>
-    <row r="65"/>
     <row r="66">
       <c r="B66" t="inlineStr">
         <is>
@@ -3784,6 +3776,119 @@
         <is>
           <t>passive_perfect_dodge_weiyi</t>
         </is>
+      </c>
+      <c r="M68" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>orb_skill_summon</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>orb_skill_summon</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>能量球召唤</t>
+        </is>
+      </c>
+      <c r="F69" t="b">
+        <v>0</v>
+      </c>
+      <c r="I69" t="b">
+        <v>0</v>
+      </c>
+      <c r="J69" t="b">
+        <v>0</v>
+      </c>
+      <c r="K69" t="b">
+        <v>1</v>
+      </c>
+      <c r="L69" t="b">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>8</v>
+      </c>
+      <c r="N69" t="n">
+        <v>1</v>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>icon_01</t>
+        </is>
+      </c>
+      <c r="P69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>player_enter_expose</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>player_enter_expose</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>蓄力进入暴露态</t>
+        </is>
+      </c>
+      <c r="F70" t="b">
+        <v>0</v>
+      </c>
+      <c r="I70" t="b">
+        <v>0</v>
+      </c>
+      <c r="J70" t="b">
+        <v>0</v>
+      </c>
+      <c r="K70" t="b">
+        <v>1</v>
+      </c>
+      <c r="L70" t="b">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>2</v>
+      </c>
+      <c r="N70" t="n">
+        <v>1</v>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>icon_01</t>
+        </is>
+      </c>
+      <c r="P70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3963,7 +4068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="27" customWidth="1" min="6" max="6"/>
@@ -4227,6 +4332,32 @@
         <v>1</v>
       </c>
     </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>能量球召唤</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>4,1,0,0,0,gold,0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>orb_skill_summon</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Config/Datas/skill.xlsx
+++ b/Config/Datas/skill.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="136">
   <si>
     <t>##var</t>
   </si>
@@ -385,22 +385,34 @@
     <t>NotInBattle,0,0,"",""</t>
   </si>
   <si>
+    <t>talent_expose_charm</t>
+  </si>
+  <si>
+    <t>talent_expose_extra_charm_1</t>
+  </si>
+  <si>
     <t>school_id</t>
   </si>
   <si>
     <t>display_name</t>
   </si>
   <si>
-    <t>sort_order</t>
-  </si>
-  <si>
-    <t>近战通用</t>
-  </si>
-  <si>
-    <t>女王体系</t>
-  </si>
-  <si>
-    <t>特殊与被动</t>
+    <t>unlock_conds</t>
+  </si>
+  <si>
+    <t>(list#sep=;),CommonCheckCond</t>
+  </si>
+  <si>
+    <t>愤怒</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>幻惑</t>
+  </si>
+  <si>
+    <t>夜幕</t>
   </si>
   <si>
     <t>entry_id</t>
@@ -410,9 +422,6 @@
   </si>
   <si>
     <t>skill_level</t>
-  </si>
-  <si>
-    <t>(list#sep=;),CommonCheckCond</t>
   </si>
   <si>
     <t>普通斩击学习</t>
@@ -1389,7 +1398,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U71"/>
+  <dimension ref="A1:U75"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="21.25" customWidth="1"/>
@@ -1398,7 +1407,7 @@
     <col min="8" max="8" width="12.125" customWidth="1"/>
     <col min="10" max="10" width="14.125" customWidth="1"/>
     <col min="13" max="13" width="22.625" customWidth="1"/>
-    <col min="14" max="14" width="17.75" customWidth="1"/>
+    <col min="14" max="15" width="17.75" customWidth="1"/>
     <col min="17" max="17" width="15.25" customWidth="1"/>
     <col min="19" max="19" width="14" customWidth="1"/>
     <col min="20" max="20" width="15.125" customWidth="1"/>
@@ -3693,148 +3702,159 @@
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="2:21">
-      <c r="B69" t="s">
-        <v>111</v>
-      </c>
-      <c r="C69" t="s">
-        <v>111</v>
-      </c>
-      <c r="E69" t="s">
-        <v>112</v>
-      </c>
-      <c r="F69" t="b">
-        <v>0</v>
-      </c>
-      <c r="I69" t="b">
-        <v>0</v>
-      </c>
-      <c r="J69" t="b">
-        <v>0</v>
-      </c>
-      <c r="K69" t="b">
-        <v>1</v>
-      </c>
-      <c r="L69" t="b">
-        <v>0</v>
-      </c>
-      <c r="M69">
-        <v>8</v>
-      </c>
-      <c r="N69">
-        <v>1</v>
-      </c>
-      <c r="O69" t="s">
-        <v>36</v>
-      </c>
-      <c r="P69">
-        <v>1</v>
-      </c>
-      <c r="Q69">
-        <v>0</v>
-      </c>
-      <c r="R69">
-        <v>0</v>
-      </c>
-      <c r="S69">
-        <v>0</v>
-      </c>
-    </row>
     <row r="70" spans="2:21">
       <c r="B70" t="s">
+        <v>111</v>
+      </c>
+      <c r="C70" t="s">
+        <v>111</v>
+      </c>
+      <c r="E70" t="s">
+        <v>112</v>
+      </c>
+      <c r="F70" t="b">
+        <v>0</v>
+      </c>
+      <c r="I70" t="b">
+        <v>0</v>
+      </c>
+      <c r="J70" t="b">
+        <v>0</v>
+      </c>
+      <c r="K70" t="b">
+        <v>1</v>
+      </c>
+      <c r="L70" t="b">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>8</v>
+      </c>
+      <c r="N70">
+        <v>1</v>
+      </c>
+      <c r="O70" t="s">
+        <v>111</v>
+      </c>
+      <c r="P70">
+        <v>1</v>
+      </c>
+      <c r="Q70">
+        <v>0</v>
+      </c>
+      <c r="R70">
+        <v>0</v>
+      </c>
+      <c r="S70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21">
+      <c r="B72" t="s">
         <v>113</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C72" t="s">
         <v>113</v>
       </c>
-      <c r="E70" t="s">
+      <c r="E72" t="s">
         <v>114</v>
       </c>
-      <c r="F70" t="b">
-        <v>0</v>
-      </c>
-      <c r="I70" t="b">
-        <v>0</v>
-      </c>
-      <c r="J70" t="b">
-        <v>0</v>
-      </c>
-      <c r="K70" t="b">
-        <v>1</v>
-      </c>
-      <c r="L70" t="b">
-        <v>0</v>
-      </c>
-      <c r="M70">
+      <c r="F72" t="b">
+        <v>0</v>
+      </c>
+      <c r="I72" t="b">
+        <v>0</v>
+      </c>
+      <c r="J72" t="b">
+        <v>0</v>
+      </c>
+      <c r="K72" t="b">
+        <v>1</v>
+      </c>
+      <c r="L72" t="b">
+        <v>0</v>
+      </c>
+      <c r="M72">
         <v>2</v>
       </c>
-      <c r="N70">
-        <v>1</v>
-      </c>
-      <c r="O70" t="s">
+      <c r="N72">
+        <v>1</v>
+      </c>
+      <c r="O72" t="s">
         <v>113</v>
       </c>
-      <c r="P70">
-        <v>1</v>
-      </c>
-      <c r="Q70">
-        <v>0</v>
-      </c>
-      <c r="R70">
-        <v>0</v>
-      </c>
-      <c r="S70">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:21">
-      <c r="B71" t="s">
+      <c r="P72">
+        <v>1</v>
+      </c>
+      <c r="Q72">
+        <v>0</v>
+      </c>
+      <c r="R72">
+        <v>0</v>
+      </c>
+      <c r="S72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21">
+      <c r="B73" t="s">
         <v>115</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C73" t="s">
         <v>115</v>
       </c>
-      <c r="E71" t="s">
+      <c r="E73" t="s">
         <v>116</v>
       </c>
-      <c r="F71" t="b">
-        <v>0</v>
-      </c>
-      <c r="I71" t="b">
-        <v>0</v>
-      </c>
-      <c r="J71" t="b">
-        <v>0</v>
-      </c>
-      <c r="K71" t="b">
-        <v>1</v>
-      </c>
-      <c r="L71" t="b">
-        <v>0</v>
-      </c>
-      <c r="M71">
+      <c r="F73" t="b">
+        <v>0</v>
+      </c>
+      <c r="I73" t="b">
+        <v>0</v>
+      </c>
+      <c r="J73" t="b">
+        <v>0</v>
+      </c>
+      <c r="K73" t="b">
+        <v>1</v>
+      </c>
+      <c r="L73" t="b">
+        <v>0</v>
+      </c>
+      <c r="M73">
         <v>2</v>
       </c>
-      <c r="N71">
-        <v>1</v>
-      </c>
-      <c r="O71" t="s">
+      <c r="N73">
+        <v>1</v>
+      </c>
+      <c r="O73" t="s">
         <v>115</v>
       </c>
-      <c r="P71">
-        <v>1</v>
-      </c>
-      <c r="Q71">
-        <v>0</v>
-      </c>
-      <c r="R71">
-        <v>0</v>
-      </c>
-      <c r="S71">
-        <v>0</v>
-      </c>
-      <c r="U71" t="s">
+      <c r="P73">
+        <v>1</v>
+      </c>
+      <c r="Q73">
+        <v>0</v>
+      </c>
+      <c r="R73">
+        <v>0</v>
+      </c>
+      <c r="S73">
+        <v>0</v>
+      </c>
+      <c r="U73" t="s">
         <v>117</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21">
+      <c r="B75" t="s">
+        <v>118</v>
+      </c>
+      <c r="F75" t="b">
+        <v>1</v>
+      </c>
+      <c r="G75" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -3846,27 +3866,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="5"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="4"/>
+  <cols>
+    <col min="3" max="3" width="12.875" customWidth="1"/>
+    <col min="4" max="4" width="11.75" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D1" t="s">
         <v>14</v>
       </c>
       <c r="E1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -3880,10 +3904,10 @@
         <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -3896,61 +3920,55 @@
       <c r="E3" t="s">
         <v>31</v>
       </c>
-      <c r="F3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>121</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>124</v>
+      </c>
+      <c r="E5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>122</v>
-      </c>
-      <c r="D6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>126</v>
+      </c>
+      <c r="E6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="B7">
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>123</v>
-      </c>
-      <c r="E7">
-        <v>30</v>
+        <v>127</v>
+      </c>
+      <c r="E7" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -3973,22 +3991,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F1" t="s">
         <v>1</v>
       </c>
       <c r="G1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4005,7 +4023,7 @@
         <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F2" t="s">
         <v>22</v>
@@ -4042,22 +4060,22 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E4" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F4" t="s">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -4068,7 +4086,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F5" t="s">
         <v>67</v>
@@ -4085,7 +4103,7 @@
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F6" t="s">
         <v>37</v>
@@ -4102,7 +4120,7 @@
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F7" t="s">
         <v>39</v>
@@ -4119,7 +4137,7 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F8" t="s">
         <v>34</v>
@@ -4139,7 +4157,7 @@
         <v>97</v>
       </c>
       <c r="E9" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F9" t="s">
         <v>96</v>
@@ -4159,7 +4177,7 @@
         <v>112</v>
       </c>
       <c r="E10" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F10" t="s">
         <v>111</v>

--- a/Config/Datas/skill.xlsx
+++ b/Config/Datas/skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17655" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="entity_skill" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="137">
   <si>
     <t>##var</t>
   </si>
@@ -391,6 +391,9 @@
     <t>talent_expose_extra_charm_1</t>
   </si>
   <si>
+    <t>grapple_hook</t>
+  </si>
+  <si>
     <t>school_id</t>
   </si>
   <si>
@@ -415,6 +418,9 @@
     <t>夜幕</t>
   </si>
   <si>
+    <t>X</t>
+  </si>
+  <si>
     <t>entry_id</t>
   </si>
   <si>
@@ -434,9 +440,6 @@
   </si>
   <si>
     <t>耐受到减伤被动</t>
-  </si>
-  <si>
-    <t>4,1,0,0,0,gold,0</t>
   </si>
 </sst>
 </file>
@@ -1398,7 +1401,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U75"/>
+  <dimension ref="A1:U77"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="21.25" customWidth="1"/>
@@ -3857,6 +3860,35 @@
         <v>119</v>
       </c>
     </row>
+    <row r="77" spans="2:21">
+      <c r="B77" t="s">
+        <v>120</v>
+      </c>
+      <c r="C77" t="s">
+        <v>120</v>
+      </c>
+      <c r="F77" t="b">
+        <v>0</v>
+      </c>
+      <c r="I77" t="b">
+        <v>0</v>
+      </c>
+      <c r="J77" t="b">
+        <v>0</v>
+      </c>
+      <c r="K77" t="b">
+        <v>1</v>
+      </c>
+      <c r="L77" t="b">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>5</v>
+      </c>
+      <c r="O77" t="s">
+        <v>120</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -3866,8 +3898,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="4"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="3" max="3" width="12.875" customWidth="1"/>
     <col min="4" max="4" width="11.75" customWidth="1"/>
@@ -3878,16 +3910,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D1" t="s">
         <v>14</v>
       </c>
       <c r="E1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3904,7 +3936,7 @@
         <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3926,16 +3958,16 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3943,10 +3975,10 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3954,10 +3986,10 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
+        <v>127</v>
+      </c>
+      <c r="E6" t="s">
         <v>126</v>
-      </c>
-      <c r="E6" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -3965,10 +3997,26 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E7" t="s">
-        <v>125</v>
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -3983,6 +4031,8 @@
   <dimension ref="A1:H10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
+    <col min="4" max="4" width="18.5" customWidth="1"/>
+    <col min="5" max="5" width="26.5" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3991,22 +4041,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F1" t="s">
         <v>1</v>
       </c>
       <c r="G1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4023,7 +4073,7 @@
         <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F2" t="s">
         <v>22</v>
@@ -4060,22 +4110,22 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F4" t="s">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -4086,7 +4136,7 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F5" t="s">
         <v>67</v>
@@ -4103,7 +4153,7 @@
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F6" t="s">
         <v>37</v>
@@ -4120,7 +4170,7 @@
         <v>2</v>
       </c>
       <c r="D7" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F7" t="s">
         <v>39</v>
@@ -4137,7 +4187,7 @@
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F8" t="s">
         <v>34</v>
@@ -4156,9 +4206,6 @@
       <c r="D9" t="s">
         <v>97</v>
       </c>
-      <c r="E9" t="s">
-        <v>135</v>
-      </c>
       <c r="F9" t="s">
         <v>96</v>
       </c>
@@ -4175,9 +4222,6 @@
       </c>
       <c r="D10" t="s">
         <v>112</v>
-      </c>
-      <c r="E10" t="s">
-        <v>135</v>
       </c>
       <c r="F10" t="s">
         <v>111</v>

--- a/Config/Datas/skill.xlsx
+++ b/Config/Datas/skill.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="1"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="entity_skill" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="142">
   <si>
     <t>##var</t>
   </si>
@@ -184,9 +184,6 @@
     <t>basic_aoe_slash</t>
   </si>
   <si>
-    <t>default_enemy_qinfan</t>
-  </si>
-  <si>
     <t>guard_attack</t>
   </si>
   <si>
@@ -394,6 +391,9 @@
     <t>grapple_hook</t>
   </si>
   <si>
+    <t>default_enemy_harass</t>
+  </si>
+  <si>
     <t>school_id</t>
   </si>
   <si>
@@ -409,9 +409,6 @@
     <t>愤怒</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>幻惑</t>
   </si>
   <si>
@@ -430,16 +427,34 @@
     <t>skill_level</t>
   </si>
   <si>
-    <t>普通斩击学习</t>
-  </si>
-  <si>
-    <t>女王普攻</t>
-  </si>
-  <si>
-    <t>女王重击</t>
+    <t>loadout_slot_type</t>
+  </si>
+  <si>
+    <t>demo.ESkillLoadoutSlotType</t>
+  </si>
+  <si>
+    <t>强化斩击</t>
+  </si>
+  <si>
+    <t>LeftClick</t>
+  </si>
+  <si>
+    <t>强化重击</t>
+  </si>
+  <si>
+    <t>RightClick</t>
   </si>
   <si>
     <t>耐受到减伤被动</t>
+  </si>
+  <si>
+    <t>Passive</t>
+  </si>
+  <si>
+    <t>召唤炮台</t>
+  </si>
+  <si>
+    <t>OtherActive</t>
   </si>
 </sst>
 </file>
@@ -1401,7 +1416,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U77"/>
+  <dimension ref="A1:U79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="21.25" customWidth="1"/>
@@ -1412,6 +1427,7 @@
     <col min="13" max="13" width="22.625" customWidth="1"/>
     <col min="14" max="15" width="17.75" customWidth="1"/>
     <col min="17" max="17" width="15.25" customWidth="1"/>
+    <col min="18" max="18" width="20.375" customWidth="1"/>
     <col min="19" max="19" width="14" customWidth="1"/>
     <col min="20" max="20" width="15.125" customWidth="1"/>
   </cols>
@@ -2262,53 +2278,12 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:21">
-      <c r="B19" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" t="s">
-        <v>51</v>
-      </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" t="b">
-        <v>0</v>
-      </c>
-      <c r="J19" t="b">
-        <v>1</v>
-      </c>
-      <c r="K19" t="b">
-        <v>1</v>
-      </c>
-      <c r="L19" t="b">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>6</v>
-      </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="P19">
-        <v>10</v>
-      </c>
-      <c r="Q19">
-        <v>0</v>
-      </c>
-      <c r="R19">
-        <v>0.8</v>
-      </c>
-      <c r="S19">
-        <v>0.1</v>
-      </c>
-    </row>
     <row r="20" spans="2:21">
       <c r="B20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F20" t="b">
         <v>0</v>
@@ -2346,10 +2321,10 @@
     </row>
     <row r="21" spans="2:21">
       <c r="B21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F21" t="b">
         <v>0</v>
@@ -2390,10 +2365,10 @@
     </row>
     <row r="22" spans="2:21">
       <c r="B22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C22" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
@@ -2431,10 +2406,10 @@
     </row>
     <row r="23" spans="2:21">
       <c r="B23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F23" t="b">
         <v>0</v>
@@ -2475,10 +2450,10 @@
     </row>
     <row r="24" spans="2:21">
       <c r="B24" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C24" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F24" t="b">
         <v>0</v>
@@ -2517,15 +2492,15 @@
         <v>0.1</v>
       </c>
       <c r="U24" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="25" spans="2:21">
       <c r="B25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C25" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F25" t="b">
         <v>0</v>
@@ -2566,10 +2541,10 @@
     </row>
     <row r="26" spans="2:21">
       <c r="B26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C26" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F26" t="b">
         <v>0</v>
@@ -2607,10 +2582,10 @@
     </row>
     <row r="27" spans="2:21">
       <c r="B27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
@@ -2648,10 +2623,10 @@
     </row>
     <row r="28" spans="2:21">
       <c r="B28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
@@ -2689,10 +2664,10 @@
     </row>
     <row r="29" spans="2:21">
       <c r="B29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F29" t="b">
         <v>0</v>
@@ -2728,15 +2703,15 @@
         <v>0.1</v>
       </c>
       <c r="U29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="2:21">
       <c r="B30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F30" t="b">
         <v>0</v>
@@ -2774,10 +2749,10 @@
     </row>
     <row r="31" spans="2:21">
       <c r="B31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F31" t="b">
         <v>0</v>
@@ -2818,10 +2793,10 @@
     </row>
     <row r="32" spans="2:21">
       <c r="B32" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" t="s">
         <v>65</v>
-      </c>
-      <c r="C32" t="s">
-        <v>66</v>
       </c>
       <c r="F32" t="b">
         <v>0</v>
@@ -2859,10 +2834,10 @@
     </row>
     <row r="33" spans="2:20">
       <c r="B33" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C33" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F33" t="b">
         <v>0</v>
@@ -2898,15 +2873,15 @@
         <v>0.1</v>
       </c>
       <c r="T33" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="34" spans="2:20">
       <c r="B34" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C34" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F34" t="b">
         <v>0</v>
@@ -2947,10 +2922,10 @@
     </row>
     <row r="36" spans="2:20">
       <c r="B36" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C36" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F36" t="b">
         <v>0</v>
@@ -2986,15 +2961,15 @@
         <v>0.1</v>
       </c>
       <c r="T36" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="38" spans="2:20">
       <c r="B38" t="s">
+        <v>70</v>
+      </c>
+      <c r="C38" t="s">
         <v>71</v>
-      </c>
-      <c r="C38" t="s">
-        <v>72</v>
       </c>
       <c r="F38" t="b">
         <v>0</v>
@@ -3032,10 +3007,10 @@
     </row>
     <row r="39" spans="2:20">
       <c r="B39" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C39" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F39" t="b">
         <v>0</v>
@@ -3073,10 +3048,10 @@
     </row>
     <row r="40" spans="2:20">
       <c r="B40" t="s">
+        <v>73</v>
+      </c>
+      <c r="C40" t="s">
         <v>74</v>
-      </c>
-      <c r="C40" t="s">
-        <v>75</v>
       </c>
       <c r="F40" t="b">
         <v>0</v>
@@ -3114,43 +3089,43 @@
     </row>
     <row r="42" spans="2:20">
       <c r="B42" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F42" t="b">
         <v>1</v>
       </c>
       <c r="G42" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="43" spans="2:20">
       <c r="B43" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F43" t="b">
         <v>1</v>
       </c>
       <c r="G43" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="44" spans="2:20">
       <c r="B44" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F44" t="b">
         <v>1</v>
       </c>
       <c r="G44" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="45" spans="2:20">
       <c r="B45" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C45" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F45" t="b">
         <v>0</v>
@@ -3188,10 +3163,10 @@
     </row>
     <row r="47" spans="2:20">
       <c r="B47" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C47" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F47" t="b">
         <v>0</v>
@@ -3229,34 +3204,34 @@
     </row>
     <row r="48" spans="2:20">
       <c r="B48" t="s">
+        <v>80</v>
+      </c>
+      <c r="C48" t="s">
+        <v>80</v>
+      </c>
+      <c r="F48" t="b">
+        <v>0</v>
+      </c>
+      <c r="I48" t="b">
+        <v>0</v>
+      </c>
+      <c r="J48" t="b">
+        <v>0</v>
+      </c>
+      <c r="K48" t="b">
+        <v>1</v>
+      </c>
+      <c r="L48" t="b">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48" t="s">
         <v>81</v>
-      </c>
-      <c r="C48" t="s">
-        <v>81</v>
-      </c>
-      <c r="F48" t="b">
-        <v>0</v>
-      </c>
-      <c r="I48" t="b">
-        <v>0</v>
-      </c>
-      <c r="J48" t="b">
-        <v>0</v>
-      </c>
-      <c r="K48" t="b">
-        <v>1</v>
-      </c>
-      <c r="L48" t="b">
-        <v>0</v>
-      </c>
-      <c r="M48">
-        <v>0</v>
-      </c>
-      <c r="N48">
-        <v>0</v>
-      </c>
-      <c r="O48" t="s">
-        <v>82</v>
       </c>
       <c r="P48">
         <v>0</v>
@@ -3273,14 +3248,14 @@
     </row>
     <row r="50" spans="2:19">
       <c r="B50" t="s">
+        <v>82</v>
+      </c>
+      <c r="C50" t="s">
+        <v>82</v>
+      </c>
+      <c r="D50" t="s">
         <v>83</v>
       </c>
-      <c r="C50" t="s">
-        <v>83</v>
-      </c>
-      <c r="D50" t="s">
-        <v>84</v>
-      </c>
       <c r="F50" t="b">
         <v>0</v>
       </c>
@@ -3303,7 +3278,7 @@
         <v>0</v>
       </c>
       <c r="O50" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P50">
         <v>0</v>
@@ -3320,17 +3295,17 @@
     </row>
     <row r="51" spans="2:19">
       <c r="B51" t="s">
+        <v>84</v>
+      </c>
+      <c r="C51" t="s">
+        <v>84</v>
+      </c>
+      <c r="D51" t="s">
         <v>85</v>
       </c>
-      <c r="C51" t="s">
-        <v>85</v>
-      </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>86</v>
       </c>
-      <c r="E51" t="s">
-        <v>87</v>
-      </c>
       <c r="F51" t="b">
         <v>0</v>
       </c>
@@ -3353,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="O51" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P51">
         <v>0</v>
@@ -3370,10 +3345,10 @@
     </row>
     <row r="52" spans="2:19">
       <c r="B52" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C52" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F52" t="b">
         <v>0</v>
@@ -3397,7 +3372,7 @@
         <v>0</v>
       </c>
       <c r="O52" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P52">
         <v>0</v>
@@ -3414,10 +3389,10 @@
     </row>
     <row r="53" spans="2:19">
       <c r="B53" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C53" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F53" t="b">
         <v>0</v>
@@ -3441,7 +3416,7 @@
         <v>0</v>
       </c>
       <c r="O53" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P53">
         <v>0</v>
@@ -3458,10 +3433,10 @@
     </row>
     <row r="54" spans="2:19">
       <c r="B54" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C54" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F54" t="b">
         <v>0</v>
@@ -3485,7 +3460,7 @@
         <v>0</v>
       </c>
       <c r="O54" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P54">
         <v>0</v>
@@ -3502,43 +3477,43 @@
     </row>
     <row r="56" spans="2:19">
       <c r="B56" t="s">
+        <v>90</v>
+      </c>
+      <c r="F56" t="b">
+        <v>1</v>
+      </c>
+      <c r="G56" t="s">
         <v>91</v>
-      </c>
-      <c r="F56" t="b">
-        <v>1</v>
-      </c>
-      <c r="G56" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="57" spans="2:19">
       <c r="B57" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F57" t="b">
         <v>1</v>
       </c>
       <c r="G57" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="58" spans="2:19">
       <c r="B58" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F58" t="b">
         <v>1</v>
       </c>
       <c r="G58" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="59" spans="2:19">
       <c r="B59" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C59" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F59" t="b">
         <v>0</v>
@@ -3576,13 +3551,13 @@
     </row>
     <row r="60" spans="2:19">
       <c r="B60" t="s">
+        <v>95</v>
+      </c>
+      <c r="C60" t="s">
+        <v>95</v>
+      </c>
+      <c r="E60" t="s">
         <v>96</v>
-      </c>
-      <c r="C60" t="s">
-        <v>96</v>
-      </c>
-      <c r="E60" t="s">
-        <v>97</v>
       </c>
       <c r="F60" t="b">
         <v>0</v>
@@ -3623,24 +3598,24 @@
     </row>
     <row r="62" spans="2:19">
       <c r="B62" t="s">
+        <v>97</v>
+      </c>
+      <c r="E62" t="s">
         <v>98</v>
       </c>
-      <c r="E62" t="s">
+      <c r="F62" t="b">
+        <v>1</v>
+      </c>
+      <c r="G62" t="s">
         <v>99</v>
-      </c>
-      <c r="F62" t="b">
-        <v>1</v>
-      </c>
-      <c r="G62" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="63" spans="2:19">
       <c r="B63" t="s">
+        <v>100</v>
+      </c>
+      <c r="C63" t="s">
         <v>101</v>
-      </c>
-      <c r="C63" t="s">
-        <v>102</v>
       </c>
       <c r="F63" t="b">
         <v>0</v>
@@ -3660,46 +3635,46 @@
     </row>
     <row r="64" spans="2:19">
       <c r="B64" t="s">
+        <v>102</v>
+      </c>
+      <c r="F64" t="b">
+        <v>1</v>
+      </c>
+      <c r="G64" t="s">
         <v>103</v>
-      </c>
-      <c r="F64" t="b">
-        <v>1</v>
-      </c>
-      <c r="G64" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="66" spans="2:21">
       <c r="B66" t="s">
+        <v>104</v>
+      </c>
+      <c r="F66" t="b">
+        <v>1</v>
+      </c>
+      <c r="G66" t="s">
         <v>105</v>
-      </c>
-      <c r="F66" t="b">
-        <v>1</v>
-      </c>
-      <c r="G66" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="67" spans="2:21">
       <c r="B67" t="s">
+        <v>106</v>
+      </c>
+      <c r="F67" t="b">
+        <v>1</v>
+      </c>
+      <c r="G67" t="s">
         <v>107</v>
-      </c>
-      <c r="F67" t="b">
-        <v>1</v>
-      </c>
-      <c r="G67" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="68" spans="2:21">
       <c r="B68" t="s">
+        <v>108</v>
+      </c>
+      <c r="F68" t="b">
+        <v>1</v>
+      </c>
+      <c r="G68" t="s">
         <v>109</v>
-      </c>
-      <c r="F68" t="b">
-        <v>1</v>
-      </c>
-      <c r="G68" t="s">
-        <v>110</v>
       </c>
       <c r="M68">
         <v>8</v>
@@ -3707,13 +3682,13 @@
     </row>
     <row r="70" spans="2:21">
       <c r="B70" t="s">
+        <v>110</v>
+      </c>
+      <c r="C70" t="s">
+        <v>110</v>
+      </c>
+      <c r="E70" t="s">
         <v>111</v>
-      </c>
-      <c r="C70" t="s">
-        <v>111</v>
-      </c>
-      <c r="E70" t="s">
-        <v>112</v>
       </c>
       <c r="F70" t="b">
         <v>0</v>
@@ -3737,7 +3712,7 @@
         <v>1</v>
       </c>
       <c r="O70" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P70">
         <v>1</v>
@@ -3754,13 +3729,13 @@
     </row>
     <row r="72" spans="2:21">
       <c r="B72" t="s">
+        <v>112</v>
+      </c>
+      <c r="C72" t="s">
+        <v>112</v>
+      </c>
+      <c r="E72" t="s">
         <v>113</v>
-      </c>
-      <c r="C72" t="s">
-        <v>113</v>
-      </c>
-      <c r="E72" t="s">
-        <v>114</v>
       </c>
       <c r="F72" t="b">
         <v>0</v>
@@ -3784,7 +3759,7 @@
         <v>1</v>
       </c>
       <c r="O72" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P72">
         <v>1</v>
@@ -3801,13 +3776,13 @@
     </row>
     <row r="73" spans="2:21">
       <c r="B73" t="s">
+        <v>114</v>
+      </c>
+      <c r="C73" t="s">
+        <v>114</v>
+      </c>
+      <c r="E73" t="s">
         <v>115</v>
-      </c>
-      <c r="C73" t="s">
-        <v>115</v>
-      </c>
-      <c r="E73" t="s">
-        <v>116</v>
       </c>
       <c r="F73" t="b">
         <v>0</v>
@@ -3831,7 +3806,7 @@
         <v>1</v>
       </c>
       <c r="O73" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P73">
         <v>1</v>
@@ -3846,26 +3821,26 @@
         <v>0</v>
       </c>
       <c r="U73" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="75" spans="2:21">
       <c r="B75" t="s">
+        <v>117</v>
+      </c>
+      <c r="F75" t="b">
+        <v>1</v>
+      </c>
+      <c r="G75" t="s">
         <v>118</v>
-      </c>
-      <c r="F75" t="b">
-        <v>1</v>
-      </c>
-      <c r="G75" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="77" spans="2:21">
       <c r="B77" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C77" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F77" t="b">
         <v>0</v>
@@ -3886,7 +3861,48 @@
         <v>5</v>
       </c>
       <c r="O77" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21">
+      <c r="B79" t="s">
         <v>120</v>
+      </c>
+      <c r="C79" t="s">
+        <v>120</v>
+      </c>
+      <c r="F79" t="b">
+        <v>0</v>
+      </c>
+      <c r="I79" t="b">
+        <v>0</v>
+      </c>
+      <c r="J79" t="b">
+        <v>1</v>
+      </c>
+      <c r="K79" t="b">
+        <v>1</v>
+      </c>
+      <c r="L79" t="b">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>6</v>
+      </c>
+      <c r="N79">
+        <v>0</v>
+      </c>
+      <c r="P79">
+        <v>10</v>
+      </c>
+      <c r="Q79">
+        <v>0</v>
+      </c>
+      <c r="R79">
+        <v>2</v>
+      </c>
+      <c r="S79">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -3977,18 +3993,12 @@
       <c r="C5" t="s">
         <v>125</v>
       </c>
-      <c r="E5" t="s">
-        <v>126</v>
-      </c>
     </row>
     <row r="6" spans="1:5">
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>127</v>
-      </c>
-      <c r="E6" t="s">
         <v>126</v>
       </c>
     </row>
@@ -3997,10 +4007,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>128</v>
-      </c>
-      <c r="E7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4008,7 +4015,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4016,7 +4023,7 @@
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -4028,12 +4035,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="4" max="4" width="18.5" customWidth="1"/>
     <col min="5" max="5" width="26.5" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
+    <col min="8" max="8" width="20.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -4041,7 +4049,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C1" t="s">
         <v>121</v>
@@ -4050,12 +4058,15 @@
         <v>122</v>
       </c>
       <c r="E1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" t="s">
         <v>131</v>
       </c>
-      <c r="F1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>132</v>
       </c>
     </row>
@@ -4081,6 +4092,9 @@
       <c r="G2" t="s">
         <v>26</v>
       </c>
+      <c r="H2" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
@@ -4110,7 +4124,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C4" t="s">
         <v>121</v>
@@ -4119,115 +4133,116 @@
         <v>122</v>
       </c>
       <c r="E4" t="s">
+        <v>130</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
         <v>131</v>
       </c>
-      <c r="F4" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F5" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="G5">
         <v>1</v>
+      </c>
+      <c r="H5" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6">
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G6">
         <v>1</v>
+      </c>
+      <c r="H6" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7">
         <v>3</v>
       </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
       <c r="D7" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G7">
         <v>1</v>
+      </c>
+      <c r="H7" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="B8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="F8" t="s">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="G8">
         <v>1</v>
+      </c>
+      <c r="H8" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="B9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="F9" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="B10">
-        <v>6</v>
-      </c>
-      <c r="C10">
-        <v>2</v>
-      </c>
-      <c r="D10" t="s">
-        <v>112</v>
-      </c>
-      <c r="F10" t="s">
-        <v>111</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
+      <c r="H9" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/skill.xlsx
+++ b/Config/Datas/skill.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="143">
   <si>
     <t>##var</t>
   </si>
@@ -241,6 +241,12 @@
     <t>default_h_attack</t>
   </si>
   <si>
+    <t>default_enemy_harass</t>
+  </si>
+  <si>
+    <t>default_enemy_knockdown_push</t>
+  </si>
+  <si>
     <t>npc_shoot_01</t>
   </si>
   <si>
@@ -389,9 +395,6 @@
   </si>
   <si>
     <t>grapple_hook</t>
-  </si>
-  <si>
-    <t>default_enemy_harass</t>
   </si>
   <si>
     <t>school_id</t>
@@ -2964,9 +2967,50 @@
         <v>67</v>
       </c>
     </row>
+    <row r="37" spans="2:20">
+      <c r="B37" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" t="s">
+        <v>70</v>
+      </c>
+      <c r="F37" t="b">
+        <v>0</v>
+      </c>
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37" t="b">
+        <v>1</v>
+      </c>
+      <c r="K37" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" t="b">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>6</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>10</v>
+      </c>
+      <c r="Q37">
+        <v>0</v>
+      </c>
+      <c r="R37">
+        <v>2</v>
+      </c>
+      <c r="S37">
+        <v>0.1</v>
+      </c>
+    </row>
     <row r="38" spans="2:20">
       <c r="B38" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C38" t="s">
         <v>71</v>
@@ -2978,7 +3022,7 @@
         <v>0</v>
       </c>
       <c r="J38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="b">
         <v>1</v>
@@ -2987,72 +3031,31 @@
         <v>0</v>
       </c>
       <c r="M38">
+        <v>12</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="P38">
         <v>10</v>
       </c>
-      <c r="N38">
-        <v>0</v>
-      </c>
-      <c r="P38">
-        <v>5</v>
-      </c>
       <c r="Q38">
         <v>0</v>
       </c>
       <c r="R38">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S38">
         <v>0.1</v>
       </c>
     </row>
-    <row r="39" spans="2:20">
-      <c r="B39" t="s">
-        <v>72</v>
-      </c>
-      <c r="C39" t="s">
-        <v>71</v>
-      </c>
-      <c r="F39" t="b">
-        <v>0</v>
-      </c>
-      <c r="I39" t="b">
-        <v>0</v>
-      </c>
-      <c r="J39" t="b">
-        <v>0</v>
-      </c>
-      <c r="K39" t="b">
-        <v>1</v>
-      </c>
-      <c r="L39" t="b">
-        <v>0</v>
-      </c>
-      <c r="M39">
-        <v>10</v>
-      </c>
-      <c r="N39">
-        <v>0</v>
-      </c>
-      <c r="P39">
-        <v>5</v>
-      </c>
-      <c r="Q39">
-        <v>0</v>
-      </c>
-      <c r="R39">
-        <v>5</v>
-      </c>
-      <c r="S39">
-        <v>0.1</v>
-      </c>
-    </row>
     <row r="40" spans="2:20">
       <c r="B40" t="s">
+        <v>72</v>
+      </c>
+      <c r="C40" t="s">
         <v>73</v>
       </c>
-      <c r="C40" t="s">
-        <v>74</v>
-      </c>
       <c r="F40" t="b">
         <v>0</v>
       </c>
@@ -3069,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="M40">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N40">
         <v>0</v>
@@ -3081,9 +3084,50 @@
         <v>0</v>
       </c>
       <c r="R40">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="S40">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="41" spans="2:20">
+      <c r="B41" t="s">
+        <v>74</v>
+      </c>
+      <c r="C41" t="s">
+        <v>73</v>
+      </c>
+      <c r="F41" t="b">
+        <v>0</v>
+      </c>
+      <c r="I41" t="b">
+        <v>0</v>
+      </c>
+      <c r="J41" t="b">
+        <v>0</v>
+      </c>
+      <c r="K41" t="b">
+        <v>1</v>
+      </c>
+      <c r="L41" t="b">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>10</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>5</v>
+      </c>
+      <c r="Q41">
+        <v>0</v>
+      </c>
+      <c r="R41">
+        <v>5</v>
+      </c>
+      <c r="S41">
         <v>0.1</v>
       </c>
     </row>
@@ -3091,22 +3135,41 @@
       <c r="B42" t="s">
         <v>75</v>
       </c>
+      <c r="C42" t="s">
+        <v>76</v>
+      </c>
       <c r="F42" t="b">
-        <v>1</v>
-      </c>
-      <c r="G42" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="43" spans="2:20">
-      <c r="B43" t="s">
-        <v>76</v>
-      </c>
-      <c r="F43" t="b">
-        <v>1</v>
-      </c>
-      <c r="G43" t="s">
-        <v>76</v>
+        <v>0</v>
+      </c>
+      <c r="I42" t="b">
+        <v>0</v>
+      </c>
+      <c r="J42" t="b">
+        <v>0</v>
+      </c>
+      <c r="K42" t="b">
+        <v>1</v>
+      </c>
+      <c r="L42" t="b">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>5</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>5</v>
+      </c>
+      <c r="Q42">
+        <v>0</v>
+      </c>
+      <c r="R42">
+        <v>1.5</v>
+      </c>
+      <c r="S42">
+        <v>0.1</v>
       </c>
     </row>
     <row r="44" spans="2:20">
@@ -3124,49 +3187,30 @@
       <c r="B45" t="s">
         <v>78</v>
       </c>
-      <c r="C45" t="s">
+      <c r="F45" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" t="s">
         <v>78</v>
       </c>
-      <c r="F45" t="b">
-        <v>0</v>
-      </c>
-      <c r="I45" t="b">
-        <v>0</v>
-      </c>
-      <c r="J45" t="b">
-        <v>0</v>
-      </c>
-      <c r="K45" t="b">
-        <v>1</v>
-      </c>
-      <c r="L45" t="b">
-        <v>0</v>
-      </c>
-      <c r="M45">
-        <v>0</v>
-      </c>
-      <c r="N45">
-        <v>0</v>
-      </c>
-      <c r="P45">
-        <v>0</v>
-      </c>
-      <c r="Q45">
-        <v>0</v>
-      </c>
-      <c r="R45">
-        <v>1</v>
-      </c>
-      <c r="S45">
-        <v>0</v>
+    </row>
+    <row r="46" spans="2:20">
+      <c r="B46" t="s">
+        <v>79</v>
+      </c>
+      <c r="F46" t="b">
+        <v>1</v>
+      </c>
+      <c r="G46" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="47" spans="2:20">
       <c r="B47" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C47" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F47" t="b">
         <v>0</v>
@@ -3196,53 +3240,50 @@
         <v>0</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S47">
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:20">
-      <c r="B48" t="s">
-        <v>80</v>
-      </c>
-      <c r="C48" t="s">
-        <v>80</v>
-      </c>
-      <c r="F48" t="b">
-        <v>0</v>
-      </c>
-      <c r="I48" t="b">
-        <v>0</v>
-      </c>
-      <c r="J48" t="b">
-        <v>0</v>
-      </c>
-      <c r="K48" t="b">
-        <v>1</v>
-      </c>
-      <c r="L48" t="b">
-        <v>0</v>
-      </c>
-      <c r="M48">
-        <v>0</v>
-      </c>
-      <c r="N48">
-        <v>0</v>
-      </c>
-      <c r="O48" t="s">
+    <row r="49" spans="2:19">
+      <c r="B49" t="s">
         <v>81</v>
       </c>
-      <c r="P48">
-        <v>0</v>
-      </c>
-      <c r="Q48">
-        <v>0</v>
-      </c>
-      <c r="R48">
-        <v>0</v>
-      </c>
-      <c r="S48">
+      <c r="C49" t="s">
+        <v>81</v>
+      </c>
+      <c r="F49" t="b">
+        <v>0</v>
+      </c>
+      <c r="I49" t="b">
+        <v>0</v>
+      </c>
+      <c r="J49" t="b">
+        <v>0</v>
+      </c>
+      <c r="K49" t="b">
+        <v>1</v>
+      </c>
+      <c r="L49" t="b">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+      <c r="Q49">
+        <v>0</v>
+      </c>
+      <c r="R49">
+        <v>0</v>
+      </c>
+      <c r="S49">
         <v>0</v>
       </c>
     </row>
@@ -3253,33 +3294,30 @@
       <c r="C50" t="s">
         <v>82</v>
       </c>
-      <c r="D50" t="s">
+      <c r="F50" t="b">
+        <v>0</v>
+      </c>
+      <c r="I50" t="b">
+        <v>0</v>
+      </c>
+      <c r="J50" t="b">
+        <v>0</v>
+      </c>
+      <c r="K50" t="b">
+        <v>1</v>
+      </c>
+      <c r="L50" t="b">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>0</v>
+      </c>
+      <c r="O50" t="s">
         <v>83</v>
       </c>
-      <c r="F50" t="b">
-        <v>0</v>
-      </c>
-      <c r="I50" t="b">
-        <v>0</v>
-      </c>
-      <c r="J50" t="b">
-        <v>0</v>
-      </c>
-      <c r="K50" t="b">
-        <v>1</v>
-      </c>
-      <c r="L50" t="b">
-        <v>0</v>
-      </c>
-      <c r="M50">
-        <v>0</v>
-      </c>
-      <c r="N50">
-        <v>0</v>
-      </c>
-      <c r="O50" t="s">
-        <v>82</v>
-      </c>
       <c r="P50">
         <v>0</v>
       </c>
@@ -3287,68 +3325,21 @@
         <v>0</v>
       </c>
       <c r="R50">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S50">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="51" spans="2:19">
-      <c r="B51" t="s">
-        <v>84</v>
-      </c>
-      <c r="C51" t="s">
-        <v>84</v>
-      </c>
-      <c r="D51" t="s">
-        <v>85</v>
-      </c>
-      <c r="E51" t="s">
-        <v>86</v>
-      </c>
-      <c r="F51" t="b">
-        <v>0</v>
-      </c>
-      <c r="I51" t="b">
-        <v>0</v>
-      </c>
-      <c r="J51" t="b">
-        <v>0</v>
-      </c>
-      <c r="K51" t="b">
-        <v>1</v>
-      </c>
-      <c r="L51" t="b">
-        <v>0</v>
-      </c>
-      <c r="M51">
-        <v>0</v>
-      </c>
-      <c r="N51">
-        <v>0</v>
-      </c>
-      <c r="O51" t="s">
-        <v>82</v>
-      </c>
-      <c r="P51">
-        <v>0</v>
-      </c>
-      <c r="Q51">
-        <v>0</v>
-      </c>
-      <c r="R51">
-        <v>3</v>
-      </c>
-      <c r="S51">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="2:19">
       <c r="B52" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C52" t="s">
-        <v>87</v>
+        <v>84</v>
+      </c>
+      <c r="D52" t="s">
+        <v>85</v>
       </c>
       <c r="F52" t="b">
         <v>0</v>
@@ -3366,13 +3357,13 @@
         <v>0</v>
       </c>
       <c r="M52">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N52">
         <v>0</v>
       </c>
       <c r="O52" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="P52">
         <v>0</v>
@@ -3389,11 +3380,17 @@
     </row>
     <row r="53" spans="2:19">
       <c r="B53" t="s">
+        <v>86</v>
+      </c>
+      <c r="C53" t="s">
+        <v>86</v>
+      </c>
+      <c r="D53" t="s">
+        <v>87</v>
+      </c>
+      <c r="E53" t="s">
         <v>88</v>
       </c>
-      <c r="C53" t="s">
-        <v>88</v>
-      </c>
       <c r="F53" t="b">
         <v>0</v>
       </c>
@@ -3410,13 +3407,13 @@
         <v>0</v>
       </c>
       <c r="M53">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N53">
         <v>0</v>
       </c>
       <c r="O53" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="P53">
         <v>0</v>
@@ -3475,173 +3472,250 @@
         <v>0.1</v>
       </c>
     </row>
+    <row r="55" spans="2:19">
+      <c r="B55" t="s">
+        <v>90</v>
+      </c>
+      <c r="C55" t="s">
+        <v>90</v>
+      </c>
+      <c r="F55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I55" t="b">
+        <v>0</v>
+      </c>
+      <c r="J55" t="b">
+        <v>0</v>
+      </c>
+      <c r="K55" t="b">
+        <v>1</v>
+      </c>
+      <c r="L55" t="b">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>4</v>
+      </c>
+      <c r="N55">
+        <v>0</v>
+      </c>
+      <c r="O55" t="s">
+        <v>90</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+      <c r="Q55">
+        <v>0</v>
+      </c>
+      <c r="R55">
+        <v>3</v>
+      </c>
+      <c r="S55">
+        <v>0.1</v>
+      </c>
+    </row>
     <row r="56" spans="2:19">
       <c r="B56" t="s">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="C56" t="s">
+        <v>91</v>
       </c>
       <c r="F56" t="b">
-        <v>1</v>
-      </c>
-      <c r="G56" t="s">
+        <v>0</v>
+      </c>
+      <c r="I56" t="b">
+        <v>0</v>
+      </c>
+      <c r="J56" t="b">
+        <v>0</v>
+      </c>
+      <c r="K56" t="b">
+        <v>1</v>
+      </c>
+      <c r="L56" t="b">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>4</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="57" spans="2:19">
-      <c r="B57" t="s">
-        <v>92</v>
-      </c>
-      <c r="F57" t="b">
-        <v>1</v>
-      </c>
-      <c r="G57" t="s">
-        <v>91</v>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <v>0</v>
+      </c>
+      <c r="R56">
+        <v>3</v>
+      </c>
+      <c r="S56">
+        <v>0.1</v>
       </c>
     </row>
     <row r="58" spans="2:19">
       <c r="B58" t="s">
+        <v>92</v>
+      </c>
+      <c r="F58" t="b">
+        <v>1</v>
+      </c>
+      <c r="G58" t="s">
         <v>93</v>
-      </c>
-      <c r="F58" t="b">
-        <v>1</v>
-      </c>
-      <c r="G58" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="59" spans="2:19">
       <c r="B59" t="s">
         <v>94</v>
       </c>
-      <c r="C59" t="s">
-        <v>94</v>
-      </c>
       <c r="F59" t="b">
-        <v>0</v>
-      </c>
-      <c r="I59" t="b">
-        <v>0</v>
-      </c>
-      <c r="J59" t="b">
-        <v>0</v>
-      </c>
-      <c r="K59" t="b">
-        <v>1</v>
-      </c>
-      <c r="L59" t="b">
-        <v>0</v>
-      </c>
-      <c r="M59">
-        <v>0</v>
-      </c>
-      <c r="N59">
-        <v>0</v>
-      </c>
-      <c r="P59">
-        <v>0</v>
-      </c>
-      <c r="Q59">
-        <v>0</v>
-      </c>
-      <c r="R59">
-        <v>0</v>
-      </c>
-      <c r="S59">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="G59" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="60" spans="2:19">
       <c r="B60" t="s">
         <v>95</v>
       </c>
-      <c r="C60" t="s">
-        <v>95</v>
-      </c>
-      <c r="E60" t="s">
+      <c r="F60" t="b">
+        <v>1</v>
+      </c>
+      <c r="G60" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="61" spans="2:19">
+      <c r="B61" t="s">
         <v>96</v>
       </c>
-      <c r="F60" t="b">
-        <v>0</v>
-      </c>
-      <c r="I60" t="b">
-        <v>0</v>
-      </c>
-      <c r="J60" t="b">
-        <v>0</v>
-      </c>
-      <c r="K60" t="b">
-        <v>1</v>
-      </c>
-      <c r="L60" t="b">
-        <v>0</v>
-      </c>
-      <c r="M60">
-        <v>8</v>
-      </c>
-      <c r="N60">
-        <v>3</v>
-      </c>
-      <c r="O60" t="s">
-        <v>36</v>
-      </c>
-      <c r="P60">
-        <v>1</v>
-      </c>
-      <c r="Q60">
-        <v>0</v>
-      </c>
-      <c r="R60">
-        <v>6</v>
-      </c>
-      <c r="S60">
-        <v>0.1</v>
+      <c r="C61" t="s">
+        <v>96</v>
+      </c>
+      <c r="F61" t="b">
+        <v>0</v>
+      </c>
+      <c r="I61" t="b">
+        <v>0</v>
+      </c>
+      <c r="J61" t="b">
+        <v>0</v>
+      </c>
+      <c r="K61" t="b">
+        <v>1</v>
+      </c>
+      <c r="L61" t="b">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>0</v>
+      </c>
+      <c r="R61">
+        <v>0</v>
+      </c>
+      <c r="S61">
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="2:19">
       <c r="B62" t="s">
         <v>97</v>
       </c>
+      <c r="C62" t="s">
+        <v>97</v>
+      </c>
       <c r="E62" t="s">
         <v>98</v>
       </c>
       <c r="F62" t="b">
-        <v>1</v>
-      </c>
-      <c r="G62" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="63" spans="2:19">
-      <c r="B63" t="s">
-        <v>100</v>
-      </c>
-      <c r="C63" t="s">
-        <v>101</v>
-      </c>
-      <c r="F63" t="b">
-        <v>0</v>
-      </c>
-      <c r="M63">
-        <v>5</v>
-      </c>
-      <c r="P63">
-        <v>10</v>
-      </c>
-      <c r="Q63">
-        <v>60</v>
-      </c>
-      <c r="R63">
-        <v>12</v>
+        <v>0</v>
+      </c>
+      <c r="I62" t="b">
+        <v>0</v>
+      </c>
+      <c r="J62" t="b">
+        <v>0</v>
+      </c>
+      <c r="K62" t="b">
+        <v>1</v>
+      </c>
+      <c r="L62" t="b">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>8</v>
+      </c>
+      <c r="N62">
+        <v>3</v>
+      </c>
+      <c r="O62" t="s">
+        <v>36</v>
+      </c>
+      <c r="P62">
+        <v>1</v>
+      </c>
+      <c r="Q62">
+        <v>0</v>
+      </c>
+      <c r="R62">
+        <v>6</v>
+      </c>
+      <c r="S62">
+        <v>0.1</v>
       </c>
     </row>
     <row r="64" spans="2:19">
       <c r="B64" t="s">
+        <v>99</v>
+      </c>
+      <c r="E64" t="s">
+        <v>100</v>
+      </c>
+      <c r="F64" t="b">
+        <v>1</v>
+      </c>
+      <c r="G64" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21">
+      <c r="B65" t="s">
         <v>102</v>
       </c>
-      <c r="F64" t="b">
-        <v>1</v>
-      </c>
-      <c r="G64" t="s">
+      <c r="C65" t="s">
         <v>103</v>
+      </c>
+      <c r="F65" t="b">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>5</v>
+      </c>
+      <c r="P65">
+        <v>10</v>
+      </c>
+      <c r="Q65">
+        <v>60</v>
+      </c>
+      <c r="R65">
+        <v>12</v>
       </c>
     </row>
     <row r="66" spans="2:21">
@@ -3655,76 +3729,40 @@
         <v>105</v>
       </c>
     </row>
-    <row r="67" spans="2:21">
-      <c r="B67" t="s">
-        <v>106</v>
-      </c>
-      <c r="F67" t="b">
-        <v>1</v>
-      </c>
-      <c r="G67" t="s">
-        <v>107</v>
-      </c>
-    </row>
     <row r="68" spans="2:21">
       <c r="B68" t="s">
+        <v>106</v>
+      </c>
+      <c r="F68" t="b">
+        <v>1</v>
+      </c>
+      <c r="G68" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21">
+      <c r="B69" t="s">
         <v>108</v>
       </c>
-      <c r="F68" t="b">
-        <v>1</v>
-      </c>
-      <c r="G68" t="s">
+      <c r="F69" t="b">
+        <v>1</v>
+      </c>
+      <c r="G69" t="s">
         <v>109</v>
-      </c>
-      <c r="M68">
-        <v>8</v>
       </c>
     </row>
     <row r="70" spans="2:21">
       <c r="B70" t="s">
         <v>110</v>
       </c>
-      <c r="C70" t="s">
-        <v>110</v>
-      </c>
-      <c r="E70" t="s">
+      <c r="F70" t="b">
+        <v>1</v>
+      </c>
+      <c r="G70" t="s">
         <v>111</v>
-      </c>
-      <c r="F70" t="b">
-        <v>0</v>
-      </c>
-      <c r="I70" t="b">
-        <v>0</v>
-      </c>
-      <c r="J70" t="b">
-        <v>0</v>
-      </c>
-      <c r="K70" t="b">
-        <v>1</v>
-      </c>
-      <c r="L70" t="b">
-        <v>0</v>
       </c>
       <c r="M70">
         <v>8</v>
-      </c>
-      <c r="N70">
-        <v>1</v>
-      </c>
-      <c r="O70" t="s">
-        <v>110</v>
-      </c>
-      <c r="P70">
-        <v>1</v>
-      </c>
-      <c r="Q70">
-        <v>0</v>
-      </c>
-      <c r="R70">
-        <v>0</v>
-      </c>
-      <c r="S70">
-        <v>0</v>
       </c>
     </row>
     <row r="72" spans="2:21">
@@ -3753,7 +3791,7 @@
         <v>0</v>
       </c>
       <c r="M72">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="N72">
         <v>1</v>
@@ -3774,64 +3812,100 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:21">
-      <c r="B73" t="s">
+    <row r="74" spans="2:21">
+      <c r="B74" t="s">
         <v>114</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C74" t="s">
         <v>114</v>
       </c>
-      <c r="E73" t="s">
+      <c r="E74" t="s">
         <v>115</v>
       </c>
-      <c r="F73" t="b">
-        <v>0</v>
-      </c>
-      <c r="I73" t="b">
-        <v>0</v>
-      </c>
-      <c r="J73" t="b">
-        <v>0</v>
-      </c>
-      <c r="K73" t="b">
-        <v>1</v>
-      </c>
-      <c r="L73" t="b">
-        <v>0</v>
-      </c>
-      <c r="M73">
+      <c r="F74" t="b">
+        <v>0</v>
+      </c>
+      <c r="I74" t="b">
+        <v>0</v>
+      </c>
+      <c r="J74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K74" t="b">
+        <v>1</v>
+      </c>
+      <c r="L74" t="b">
+        <v>0</v>
+      </c>
+      <c r="M74">
         <v>2</v>
       </c>
-      <c r="N73">
-        <v>1</v>
-      </c>
-      <c r="O73" t="s">
+      <c r="N74">
+        <v>1</v>
+      </c>
+      <c r="O74" t="s">
         <v>114</v>
       </c>
-      <c r="P73">
-        <v>1</v>
-      </c>
-      <c r="Q73">
-        <v>0</v>
-      </c>
-      <c r="R73">
-        <v>0</v>
-      </c>
-      <c r="S73">
-        <v>0</v>
-      </c>
-      <c r="U73" t="s">
-        <v>116</v>
+      <c r="P74">
+        <v>1</v>
+      </c>
+      <c r="Q74">
+        <v>0</v>
+      </c>
+      <c r="R74">
+        <v>0</v>
+      </c>
+      <c r="S74">
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="2:21">
       <c r="B75" t="s">
+        <v>116</v>
+      </c>
+      <c r="C75" t="s">
+        <v>116</v>
+      </c>
+      <c r="E75" t="s">
         <v>117</v>
       </c>
       <c r="F75" t="b">
-        <v>1</v>
-      </c>
-      <c r="G75" t="s">
+        <v>0</v>
+      </c>
+      <c r="I75" t="b">
+        <v>0</v>
+      </c>
+      <c r="J75" t="b">
+        <v>0</v>
+      </c>
+      <c r="K75" t="b">
+        <v>1</v>
+      </c>
+      <c r="L75" t="b">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>2</v>
+      </c>
+      <c r="N75">
+        <v>1</v>
+      </c>
+      <c r="O75" t="s">
+        <v>116</v>
+      </c>
+      <c r="P75">
+        <v>1</v>
+      </c>
+      <c r="Q75">
+        <v>0</v>
+      </c>
+      <c r="R75">
+        <v>0</v>
+      </c>
+      <c r="S75">
+        <v>0</v>
+      </c>
+      <c r="U75" t="s">
         <v>118</v>
       </c>
     </row>
@@ -3839,37 +3913,19 @@
       <c r="B77" t="s">
         <v>119</v>
       </c>
-      <c r="C77" t="s">
-        <v>119</v>
-      </c>
       <c r="F77" t="b">
-        <v>0</v>
-      </c>
-      <c r="I77" t="b">
-        <v>0</v>
-      </c>
-      <c r="J77" t="b">
-        <v>0</v>
-      </c>
-      <c r="K77" t="b">
-        <v>1</v>
-      </c>
-      <c r="L77" t="b">
-        <v>0</v>
-      </c>
-      <c r="M77">
-        <v>5</v>
-      </c>
-      <c r="O77" t="s">
-        <v>119</v>
+        <v>1</v>
+      </c>
+      <c r="G77" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="79" spans="2:21">
       <c r="B79" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C79" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F79" t="b">
         <v>0</v>
@@ -3878,7 +3934,7 @@
         <v>0</v>
       </c>
       <c r="J79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K79" t="b">
         <v>1</v>
@@ -3887,22 +3943,10 @@
         <v>0</v>
       </c>
       <c r="M79">
-        <v>6</v>
-      </c>
-      <c r="N79">
-        <v>0</v>
-      </c>
-      <c r="P79">
-        <v>10</v>
-      </c>
-      <c r="Q79">
-        <v>0</v>
-      </c>
-      <c r="R79">
-        <v>2</v>
-      </c>
-      <c r="S79">
-        <v>0.1</v>
+        <v>5</v>
+      </c>
+      <c r="O79" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -3926,16 +3970,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D1" t="s">
         <v>14</v>
       </c>
       <c r="E1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -3952,7 +3996,7 @@
         <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3974,16 +4018,16 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3991,7 +4035,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3999,7 +4043,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4007,7 +4051,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4015,7 +4059,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4023,7 +4067,7 @@
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -4049,25 +4093,25 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F1" t="s">
         <v>1</v>
       </c>
       <c r="G1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -4084,7 +4128,7 @@
         <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F2" t="s">
         <v>22</v>
@@ -4093,7 +4137,7 @@
         <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4124,25 +4168,25 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F4" t="s">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -4153,7 +4197,7 @@
         <v>2</v>
       </c>
       <c r="D5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F5" t="s">
         <v>37</v>
@@ -4162,7 +4206,7 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -4173,7 +4217,7 @@
         <v>2</v>
       </c>
       <c r="D6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F6" t="s">
         <v>39</v>
@@ -4182,7 +4226,7 @@
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -4193,7 +4237,7 @@
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F7" t="s">
         <v>34</v>
@@ -4202,7 +4246,7 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -4213,16 +4257,16 @@
         <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="G8">
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -4233,16 +4277,16 @@
         <v>2</v>
       </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F9" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G9">
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/skill.xlsx
+++ b/Config/Datas/skill.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="entity_skill" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="skill_school" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="skill_learn" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="skill_level" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="entity_skill" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_school" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_learn" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_level" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1034,7 +1034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S80"/>
+  <dimension ref="A1:S82"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="21.25" customWidth="1" min="2" max="2"/>
@@ -3904,6 +3904,110 @@
         <is>
           <t>UnarmedFallbackOnly,0,0,"",""</t>
         </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>hit_attach</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>hit_attach</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>挣脱附着物</t>
+        </is>
+      </c>
+      <c r="F81" t="b">
+        <v>0</v>
+      </c>
+      <c r="I81" t="b">
+        <v>0</v>
+      </c>
+      <c r="J81" t="b">
+        <v>0</v>
+      </c>
+      <c r="K81" t="b">
+        <v>1</v>
+      </c>
+      <c r="L81" t="b">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>icon_01</t>
+        </is>
+      </c>
+      <c r="O81" t="n">
+        <v>100</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>forest_fly_attach</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>forest_fly_attach</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>飞虫冲刺附着</t>
+        </is>
+      </c>
+      <c r="F82" t="b">
+        <v>0</v>
+      </c>
+      <c r="I82" t="b">
+        <v>0</v>
+      </c>
+      <c r="J82" t="b">
+        <v>0</v>
+      </c>
+      <c r="K82" t="b">
+        <v>1</v>
+      </c>
+      <c r="L82" t="b">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>icon_01</t>
+        </is>
+      </c>
+      <c r="O82" t="n">
+        <v>30</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -4401,7 +4505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="18.375" customWidth="1" min="2" max="2"/>
@@ -5399,6 +5503,32 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>hit_attach</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>forest_fly_attach</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Config/Datas/skill.xlsx
+++ b/Config/Datas/skill.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="entity_skill" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_school" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_learn" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="skill_level" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="entity_skill" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="skill_school" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="skill_learn" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="skill_level" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1034,7 +1034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S82"/>
+  <dimension ref="A1:S85"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="21.25" customWidth="1" min="2" max="2"/>
@@ -4007,6 +4007,162 @@
         <v>0.8</v>
       </c>
       <c r="R82" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>treant_summon_root_nodes</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>treant_summon_root_nodes</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>treant_summon_root_nodes</t>
+        </is>
+      </c>
+      <c r="F83" t="b">
+        <v>0</v>
+      </c>
+      <c r="I83" t="b">
+        <v>0</v>
+      </c>
+      <c r="J83" t="b">
+        <v>0</v>
+      </c>
+      <c r="K83" t="b">
+        <v>1</v>
+      </c>
+      <c r="L83" t="b">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>icon_01</t>
+        </is>
+      </c>
+      <c r="O83" t="n">
+        <v>20</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>6</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>treant_summon_thorn_vines</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>treant_summon_thorn_vines</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>treant_summon_thorn_vines</t>
+        </is>
+      </c>
+      <c r="F84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I84" t="b">
+        <v>0</v>
+      </c>
+      <c r="J84" t="b">
+        <v>0</v>
+      </c>
+      <c r="K84" t="b">
+        <v>1</v>
+      </c>
+      <c r="L84" t="b">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>1</v>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>icon_01</t>
+        </is>
+      </c>
+      <c r="O84" t="n">
+        <v>30</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>6</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>treant_corrosive_barrage</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>treant_corrosive_barrage</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>treant_corrosive_barrage</t>
+        </is>
+      </c>
+      <c r="F85" t="b">
+        <v>0</v>
+      </c>
+      <c r="I85" t="b">
+        <v>0</v>
+      </c>
+      <c r="J85" t="b">
+        <v>0</v>
+      </c>
+      <c r="K85" t="b">
+        <v>1</v>
+      </c>
+      <c r="L85" t="b">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>icon_01</t>
+        </is>
+      </c>
+      <c r="O85" t="n">
+        <v>20</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>7</v>
+      </c>
+      <c r="R85" t="n">
         <v>0.1</v>
       </c>
     </row>
@@ -4505,7 +4661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="18.375" customWidth="1" min="2" max="2"/>
@@ -5529,6 +5685,45 @@
         <v>1.5</v>
       </c>
     </row>
+    <row r="71">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>treant_summon_root_nodes</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>treant_summon_thorn_vines</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>treant_corrosive_barrage</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
